--- a/erp-server/erp-server-plm/src/main/resources/excel/skuStdRetailPriceTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/skuStdRetailPriceTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -100,26 +100,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>税率</t>
-    </r>
+    <t>税率</t>
   </si>
 </sst>
 </file>
@@ -740,12 +721,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1113,7 +1097,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
